--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BFB36E6-C389-AF41-BA45-88E00EBE32C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B0699D-F6E9-D346-B14F-41CE9CD6EF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2440" yWindow="16140" windowWidth="46520" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>source:</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Opus link(s):</t>
-  </si>
-  <si>
-    <t>xxxxx</t>
   </si>
   <si>
     <t>Case #, link</t>
@@ -181,9 +178,6 @@
     <t>reference date:</t>
   </si>
   <si>
-    <t>YYYY-YYYY</t>
-  </si>
-  <si>
     <t>{parent.parent.id}</t>
   </si>
   <si>
@@ -191,6 +185,15 @@
   </si>
   <si>
     <t>CC medium priority (C3):</t>
+  </si>
+  <si>
+    <t>{doc_url:doc_link}</t>
+  </si>
+  <si>
+    <t>{edit:nonexistent}</t>
+  </si>
+  <si>
+    <t>{dates}</t>
   </si>
 </sst>
 </file>
@@ -200,7 +203,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmm\ yyyy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,12 +264,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -323,8 +320,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,12 +409,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -470,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -502,7 +508,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -511,19 +517,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -544,7 +550,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -553,13 +559,13 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -571,8 +577,8 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -603,7 +609,7 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -615,42 +621,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,7 +878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA3E779-7896-0447-95DE-6B7CBF9B99B8}">
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
@@ -882,32 +893,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D1" s="39"/>
       <c r="E1" s="40"/>
       <c r="F1" s="41"/>
       <c r="G1" s="42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" s="43"/>
       <c r="J1" s="40"/>
       <c r="K1" s="44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M1" s="45"/>
       <c r="N1" s="44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O1" s="45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P1" s="39"/>
       <c r="Q1" s="41"/>
@@ -925,7 +936,7 @@
     </row>
     <row r="2" spans="1:28" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -939,12 +950,6 @@
       <c r="K2" s="6"/>
       <c r="L2" s="47"/>
       <c r="M2" s="48"/>
-      <c r="N2" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" s="34" t="s">
-        <v>26</v>
-      </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="49"/>
@@ -961,14 +966,14 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="8"/>
@@ -979,12 +984,6 @@
       <c r="K3" s="9"/>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
-      <c r="N3" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="35" t="s">
-        <v>27</v>
-      </c>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="7"/>
@@ -1003,8 +1002,8 @@
       <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="51" t="s">
-        <v>5</v>
+      <c r="B4" s="62" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="1"/>
@@ -1082,49 +1081,49 @@
     </row>
     <row r="6" spans="1:28" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>7</v>
       </c>
       <c r="C6" s="26" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>10</v>
       </c>
       <c r="G6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="J6" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="K6" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="K6" s="53" t="s">
+      <c r="L6" s="52" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="54" t="s">
+      <c r="O6" s="54" t="s">
         <v>15</v>
-      </c>
-      <c r="O6" s="55" t="s">
-        <v>16</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -1141,50 +1140,50 @@
       <c r="AB6" s="50"/>
     </row>
     <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="56" t="s">
+      <c r="A7" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="C7" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="58" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="59" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="61" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="59" t="s">
-        <v>25</v>
+      <c r="D7" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="61" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="58" t="s">
+        <v>24</v>
       </c>
       <c r="P7" s="18"/>
       <c r="Q7" s="18"/>
@@ -1230,12 +1229,12 @@
         <v>#NAME?</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="29" t="e" cm="1">
         <f t="array" ref="F9">COUNTIF(__COL__,"C1")</f>
@@ -1266,7 +1265,7 @@
       <c r="C10" s="25"/>
       <c r="D10" s="29"/>
       <c r="E10" s="30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="29" t="e" cm="1">
         <f t="array" ref="F10">COUNTIF(__COL__,"C2")</f>
@@ -1297,7 +1296,7 @@
       <c r="C11" s="25"/>
       <c r="D11" s="29"/>
       <c r="E11" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F11" s="29" t="e" cm="1">
         <f t="array" ref="F11">COUNTIF(__COL__,"C3")</f>
@@ -1322,6 +1321,36 @@
       <c r="X11" s="25"/>
       <c r="Y11" s="25"/>
     </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="N13" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="34"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="N14" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="35"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="N15" s="34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="N16" s="63" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="14:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="64" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="14:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="65"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" display="https://uk.wikisource.org/wiki/xxxxxx" xr:uid="{38FD7A35-6AE5-E540-8766-A4F99F1AEF2E}"/>

--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B0699D-F6E9-D346-B14F-41CE9CD6EF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D97CDD8-0799-A54E-9639-6557C44B23C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2440" yWindow="16140" windowWidth="46520" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="{shortname}" sheetId="4" r:id="rId1"/>

--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D97CDD8-0799-A54E-9639-6557C44B23C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53973DCC-1918-0B44-9C52-58588C3C4058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24360" yWindow="22640" windowWidth="31580" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="{shortname}" sheetId="4" r:id="rId1"/>
@@ -32,30 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>source:</t>
   </si>
@@ -194,6 +172,45 @@
   </si>
   <si>
     <t>{dates}</t>
+  </si>
+  <si>
+    <t>=ROWS($A$__FIRST__:$A__LAST__)</t>
+  </si>
+  <si>
+    <t>Future cases to explore (FX):</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTIF($F$__FIRST__:$F__LAST__,"FX")</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTIF($F$__FIRST__:$F__LAST__,"C3")</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTIF($F$__FIRST__:$F__LAST__,"C2")</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTIF($F$__FIRST__:$F__LAST__,"C1")</t>
+  </si>
+  <si>
+    <t>__EQ__SUM(J$__FIRST__:J__LAST__)</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTA(I$__FIRST__:I__LAST__)</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTA(N$__FIRST__:N__LAST__)</t>
+  </si>
+  <si>
+    <t>__EQ__SUM(M$__FIRST__:M__LAST__)</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTA(L$__FIRST__:L__LAST__)</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTA(K$__FIRST__:K__LAST__)-COUNTIF(K$__FIRST__:K__LAST__,"")</t>
+  </si>
+  <si>
+    <t>__EQ__COUNTA(H$__FIRST__:H__LAST__)-COUNTIF(H$__FIRST__:H__LAST__,"")</t>
   </si>
 </sst>
 </file>
@@ -476,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -662,6 +679,9 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1039,33 +1059,26 @@
       <c r="G5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="22" t="e" cm="1">
-        <f t="array" ref="H5">COUNTA(__COL__)-COUNTIF(__COL__,"")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="I5" s="22">
-        <f>COUNTA(__COL__)</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="22" t="e">
-        <f>SUM(__COL__)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="K5" s="23" t="e" cm="1">
-        <f t="array" ref="K5">COUNTA(__COL__)-COUNTIF(__COL__,"")</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L5" s="23">
-        <f>COUNTA(__COL__)</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="23" t="e">
-        <f>SUM(__COL__)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="N5" s="24">
-        <f>COUNTA(__COL__)</f>
-        <v>1</v>
+      <c r="H5" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="N5" s="24" t="s">
+        <v>48</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="7"/>
@@ -1224,9 +1237,8 @@
       <c r="Y8" s="25"/>
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="e">
-        <f>ROWS(__COL__)</f>
-        <v>#NAME?</v>
+      <c r="A9" s="66" t="s">
+        <v>40</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>16</v>
@@ -1236,9 +1248,8 @@
       <c r="E9" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="29" t="e" cm="1">
-        <f t="array" ref="F9">COUNTIF(__COL__,"C1")</f>
-        <v>#NAME?</v>
+      <c r="F9" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
@@ -1267,9 +1278,8 @@
       <c r="E10" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="29" t="e" cm="1">
-        <f t="array" ref="F10">COUNTIF(__COL__,"C2")</f>
-        <v>#NAME?</v>
+      <c r="F10" s="29" t="s">
+        <v>44</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
@@ -1298,9 +1308,8 @@
       <c r="E11" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="29" t="e" cm="1">
-        <f t="array" ref="F11">COUNTIF(__COL__,"C3")</f>
-        <v>#NAME?</v>
+      <c r="F11" s="29" t="s">
+        <v>43</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
@@ -1321,6 +1330,14 @@
       <c r="X11" s="25"/>
       <c r="Y11" s="25"/>
     </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="E12" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="N13" s="32" t="s">
         <v>22</v>

--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53973DCC-1918-0B44-9C52-58588C3C4058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1376F2-A92B-2C4E-BB23-303C9D5E4084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24360" yWindow="22640" windowWidth="31580" windowHeight="10620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35160" yWindow="15160" windowWidth="34780" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="{shortname}" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>source:</t>
   </si>
@@ -211,6 +211,12 @@
   </si>
   <si>
     <t>__EQ__COUNTA(H$__FIRST__:H__LAST__)-COUNTIF(H$__FIRST__:H__LAST__,"")</t>
+  </si>
+  <si>
+    <t>{col}=IF($F7="P1",CONCATENATE($A$1,"-",$G$1,"-",$H$1,"-",$A7),"")</t>
+  </si>
+  <si>
+    <t>{col}=IF($F7="P2",CONCATENATE($A$1,"-",$G$1,"-",$H$1,"-",$A7),"")</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1181,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="I7" s="60" t="s">
         <v>24</v>
@@ -1183,8 +1189,8 @@
       <c r="J7" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="59" t="s">
-        <v>24</v>
+      <c r="K7" s="60" t="s">
+        <v>54</v>
       </c>
       <c r="L7" s="60" t="s">
         <v>24</v>

--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1376F2-A92B-2C4E-BB23-303C9D5E4084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3FC5E3-D651-234F-AD37-0FB6578EBDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35160" yWindow="15160" windowWidth="34780" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,9 +156,6 @@
     <t>reference date:</t>
   </si>
   <si>
-    <t>{parent.parent.id}</t>
-  </si>
-  <si>
     <t>{unquoted_url:linked}</t>
   </si>
   <si>
@@ -217,6 +214,9 @@
   </si>
   <si>
     <t>{col}=IF($F7="P2",CONCATENATE($A$1,"-",$G$1,"-",$H$1,"-",$A7),"")</t>
+  </si>
+  <si>
+    <t>{archive_name}</t>
   </si>
 </sst>
 </file>
@@ -919,7 +919,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
@@ -992,14 +992,14 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="8"/>
@@ -1029,7 +1029,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="1"/>
@@ -1066,25 +1066,25 @@
         <v>1</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="24" t="s">
         <v>47</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5" s="24" t="s">
-        <v>48</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="7"/>
@@ -1181,7 +1181,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" s="60" t="s">
         <v>24</v>
@@ -1190,7 +1190,7 @@
         <v>24</v>
       </c>
       <c r="K7" s="60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L7" s="60" t="s">
         <v>24</v>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>16</v>
@@ -1255,7 +1255,7 @@
         <v>17</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
@@ -1285,7 +1285,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
@@ -1312,10 +1312,10 @@
       <c r="C11" s="25"/>
       <c r="D11" s="29"/>
       <c r="E11" s="30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
@@ -1338,10 +1338,10 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="E12" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="29" t="s">
         <v>41</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -1368,7 +1368,7 @@
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N17" s="64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="14:14" x14ac:dyDescent="0.2">

--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3FC5E3-D651-234F-AD37-0FB6578EBDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C5BCD4-F348-B04D-889A-F4909673E249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35160" yWindow="15160" windowWidth="34780" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="{shortname}" sheetId="4" r:id="rId1"/>
+    <sheet name="{display_name}" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/resources/xlsx_templates/opus.xlsx
+++ b/resources/xlsx_templates/opus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbrandt/code/birddog/resources/xlsx_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C5BCD4-F348-B04D-889A-F4909673E249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E495DC3-5313-D645-BB5A-7A9D37BA7F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23760" yWindow="14340" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="{display_name}" sheetId="4" r:id="rId1"/>
@@ -111,12 +111,6 @@
     <t>CC medium priority (C2):</t>
   </si>
   <si>
-    <t>{id}</t>
-  </si>
-  <si>
-    <t>{parent.id}</t>
-  </si>
-  <si>
     <t>{description}</t>
   </si>
   <si>
@@ -217,6 +211,12 @@
   </si>
   <si>
     <t>{archive_name}</t>
+  </si>
+  <si>
+    <t>{parent.id:transliterated}</t>
+  </si>
+  <si>
+    <t>{id:transliterated}</t>
   </si>
 </sst>
 </file>
@@ -919,32 +919,32 @@
   <sheetData>
     <row r="1" spans="1:28" ht="28" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D1" s="39"/>
       <c r="E1" s="40"/>
       <c r="F1" s="41"/>
       <c r="G1" s="42" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="I1" s="43"/>
       <c r="J1" s="40"/>
       <c r="K1" s="44" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M1" s="45"/>
       <c r="N1" s="44" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O1" s="45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P1" s="39"/>
       <c r="Q1" s="41"/>
@@ -962,7 +962,7 @@
     </row>
     <row r="2" spans="1:28" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -992,14 +992,14 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="8"/>
@@ -1029,7 +1029,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="1"/>
@@ -1066,25 +1066,25 @@
         <v>1</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I5" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="N5" s="24" t="s">
         <v>45</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="24" t="s">
-        <v>47</v>
       </c>
       <c r="O5" s="17"/>
       <c r="P5" s="7"/>
@@ -1160,49 +1160,49 @@
     </row>
     <row r="7" spans="1:28" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="56" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>29</v>
-      </c>
       <c r="D7" s="57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H7" s="59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I7" s="60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J7" s="60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K7" s="60" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L7" s="60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M7" s="60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N7" s="61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O7" s="58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P7" s="18"/>
       <c r="Q7" s="18"/>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="9" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="66" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>16</v>
@@ -1255,7 +1255,7 @@
         <v>17</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G9" s="29"/>
       <c r="H9" s="29"/>
@@ -1285,7 +1285,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G10" s="29"/>
       <c r="H10" s="29"/>
@@ -1312,10 +1312,10 @@
       <c r="C11" s="25"/>
       <c r="D11" s="29"/>
       <c r="E11" s="30" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
@@ -1338,37 +1338,37 @@
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="E12" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F12" s="29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="N13" s="32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O13" s="34"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="N14" s="33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O14" s="35"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="N15" s="34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="N16" s="63" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N17" s="64" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="14:14" x14ac:dyDescent="0.2">
